--- a/src/attributions/attributions_saliency_traj_169.xlsx
+++ b/src/attributions/attributions_saliency_traj_169.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,1140 +999,7968 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.249092282610945e-06</v>
+        <v>0.01575491577386856</v>
       </c>
       <c r="B2" t="n">
-        <v>2.415864400973078e-05</v>
+        <v>0.1798070073127747</v>
       </c>
       <c r="C2" t="n">
-        <v>6.054946425138041e-06</v>
+        <v>0.1807003021240234</v>
       </c>
       <c r="D2" t="n">
-        <v>4.241318310960196e-05</v>
+        <v>0.2990255951881409</v>
       </c>
       <c r="E2" t="n">
-        <v>8.651788448332809e-06</v>
+        <v>0.187420129776001</v>
       </c>
       <c r="F2" t="n">
-        <v>8.457992407784332e-06</v>
+        <v>0.02751346305012703</v>
       </c>
       <c r="G2" t="n">
-        <v>6.995150215516333e-06</v>
+        <v>0.002958649769425392</v>
       </c>
       <c r="H2" t="n">
-        <v>1.929143536472111e-06</v>
+        <v>0.06937987357378006</v>
       </c>
       <c r="I2" t="n">
-        <v>1.549610033180215e-06</v>
+        <v>0.02427838742733002</v>
       </c>
       <c r="J2" t="n">
-        <v>1.142101609730162e-05</v>
+        <v>0.00680842250585556</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2868278392707e-05</v>
+        <v>0.1995682865381241</v>
       </c>
       <c r="L2" t="n">
-        <v>2.692956059036078e-06</v>
+        <v>0.124264732003212</v>
       </c>
       <c r="M2" t="n">
-        <v>3.984001523349434e-05</v>
+        <v>0.2528291642665863</v>
       </c>
       <c r="N2" t="n">
-        <v>1.562104216645821e-06</v>
+        <v>0.2493690699338913</v>
       </c>
       <c r="O2" t="n">
-        <v>2.473822314641438e-05</v>
+        <v>0.04483736678957939</v>
       </c>
       <c r="P2" t="n">
-        <v>5.079222319182009e-06</v>
+        <v>0.04383154958486557</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.364180570817553e-05</v>
+        <v>0.1272415071725845</v>
       </c>
       <c r="R2" t="n">
-        <v>1.328061625827104e-05</v>
+        <v>0.01688407734036446</v>
       </c>
       <c r="S2" t="n">
-        <v>5.82255597691983e-06</v>
+        <v>0.01771611534059048</v>
       </c>
       <c r="T2" t="n">
-        <v>8.770181011641398e-06</v>
+        <v>0.07544619590044022</v>
       </c>
       <c r="U2" t="n">
-        <v>2.206525323344977e-06</v>
+        <v>0.004331346601247787</v>
       </c>
       <c r="V2" t="n">
-        <v>2.930267783085583e-06</v>
+        <v>0.1009616404771805</v>
       </c>
       <c r="W2" t="n">
-        <v>8.441198588116094e-06</v>
+        <v>0.05534178391098976</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05556455309852e-05</v>
+        <v>0.08021252602338791</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.739532081046491e-06</v>
+        <v>0.06382079422473907</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.972760391159682e-06</v>
+        <v>0.01678863912820816</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.491688863097806e-06</v>
+        <v>0.1339258998632431</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.43927773530595e-06</v>
+        <v>0.0885535404086113</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.299015123862773e-06</v>
+        <v>0.1167435869574547</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.254780045201187e-06</v>
+        <v>0.08154746890068054</v>
       </c>
       <c r="AE2" t="n">
-        <v>8.400967999477871e-06</v>
+        <v>0.009895030409097672</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.893655280582607e-05</v>
+        <v>0.02510115876793861</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.510722081045969e-06</v>
+        <v>0.0248466432094574</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.569587766425684e-06</v>
+        <v>0.05781878903508186</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.872808520100079e-06</v>
+        <v>0.06317280232906342</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7.161592293414287e-06</v>
+        <v>0.05946393311023712</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.973217750783078e-06</v>
+        <v>0.03845274820923805</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.383988364977995e-05</v>
+        <v>0.1150161623954773</v>
       </c>
       <c r="AM2" t="n">
-        <v>7.62643708185351e-07</v>
+        <v>0.0520937591791153</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.516678473009961e-06</v>
+        <v>0.0285860113799572</v>
       </c>
       <c r="AO2" t="n">
-        <v>7.305948201974388e-07</v>
+        <v>0.2150548547506332</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.280896180513082e-06</v>
+        <v>0.02032643370330334</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.517989517196838e-06</v>
+        <v>0.03040983155369759</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.343684855077299e-06</v>
+        <v>0.01157416868954897</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.678174380183918e-06</v>
+        <v>0.05941438674926758</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.489326213137247e-06</v>
+        <v>0.0191483311355114</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.152125817810884e-06</v>
+        <v>0.2202720195055008</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.256222940872249e-07</v>
+        <v>0.02737045660614967</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.086210224661045e-05</v>
+        <v>0.1037072092294693</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.354401532211341e-06</v>
+        <v>0.139279380440712</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.665221008006483e-06</v>
+        <v>0.05025353655219078</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.08586094333441e-06</v>
+        <v>0.05719378590583801</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.083187044059741e-06</v>
+        <v>0.03457250073552132</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.029137016914319e-06</v>
+        <v>0.07644767314195633</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.15779124346227e-07</v>
+        <v>0.04846496880054474</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.065899596142117e-05</v>
+        <v>0.2193683981895447</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.216615136305336e-06</v>
+        <v>0.142591267824173</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.567389517731499e-05</v>
+        <v>0.1230792552232742</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.01955992654257e-07</v>
+        <v>0.2487363964319229</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.219180820859037e-06</v>
+        <v>0.03312080353498459</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.79165658664715e-06</v>
+        <v>0.03624006360769272</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.461797390031279e-08</v>
+        <v>0.09460611641407013</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.151674602326239e-06</v>
+        <v>0.06303389370441437</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.374896328343311e-05</v>
+        <v>0.005271477624773979</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.216459440911422e-05</v>
+        <v>0.1128978580236435</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.234216142620426e-07</v>
+        <v>0.01224911957979202</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.039591663560714e-06</v>
+        <v>0.09660130739212036</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.397955884385738e-07</v>
+        <v>0.09649273753166199</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.082345988834277e-06</v>
+        <v>0.0264880582690239</v>
       </c>
       <c r="BR2" t="n">
-        <v>2.742144260992063e-06</v>
+        <v>0.08279682695865631</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.706694433778466e-06</v>
+        <v>0.009209355339407921</v>
       </c>
       <c r="BT2" t="n">
-        <v>2.872347977245227e-06</v>
+        <v>0.004220265429466963</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.37820368562825e-06</v>
+        <v>0.02086459659039974</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.107449841394555e-06</v>
+        <v>0.2626081705093384</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.815732144284993e-09</v>
+        <v>0.01364553160965443</v>
       </c>
       <c r="BX2" t="n">
-        <v>7.418372206302593e-06</v>
+        <v>0.09437128901481628</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.355423233297188e-06</v>
+        <v>0.0008856570348143578</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.048854862048756e-06</v>
+        <v>0.04390234500169754</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.839042503590463e-06</v>
+        <v>0.09861528873443604</v>
       </c>
       <c r="CB2" t="n">
-        <v>1.748751174091012e-06</v>
+        <v>0.04870875179767609</v>
       </c>
       <c r="CC2" t="n">
-        <v>7.308630756597267e-06</v>
+        <v>0.1375202089548111</v>
       </c>
       <c r="CD2" t="n">
-        <v>7.425832336593885e-06</v>
+        <v>0.01010913588106632</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.497683570050867e-06</v>
+        <v>0.09497919678688049</v>
       </c>
       <c r="CF2" t="n">
-        <v>4.670127111694455e-07</v>
+        <v>0.04905884712934494</v>
       </c>
       <c r="CG2" t="n">
-        <v>1.099747532862239e-05</v>
+        <v>0.09885558485984802</v>
       </c>
       <c r="CH2" t="n">
-        <v>3.238286126361345e-06</v>
+        <v>0.02521173469722271</v>
       </c>
       <c r="CI2" t="n">
-        <v>4.766513939102879e-06</v>
+        <v>0.002163257682695985</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.778048158485035e-06</v>
+        <v>0.01284053735435009</v>
       </c>
       <c r="CK2" t="n">
-        <v>3.15346073875844e-06</v>
+        <v>0.03192795440554619</v>
       </c>
       <c r="CL2" t="n">
-        <v>5.990908107378345e-07</v>
+        <v>0.009280150756239891</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.561143557817559e-06</v>
+        <v>0.03710999339818954</v>
       </c>
       <c r="CN2" t="n">
-        <v>4.653263658838114e-07</v>
+        <v>0.03965713083744049</v>
       </c>
       <c r="CO2" t="n">
-        <v>2.053821390290977e-06</v>
+        <v>0.01756814494729042</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.026516656565946e-05</v>
+        <v>0.05093918740749359</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.604060682642739e-06</v>
+        <v>0.01057061925530434</v>
       </c>
       <c r="CR2" t="n">
-        <v>9.832136527165858e-08</v>
+        <v>0.02648812159895897</v>
       </c>
       <c r="CS2" t="n">
-        <v>1.362735474685906e-05</v>
+        <v>0.06904859095811844</v>
       </c>
       <c r="CT2" t="n">
-        <v>1.384624829370296e-05</v>
+        <v>0.06438717246055603</v>
       </c>
       <c r="CU2" t="n">
-        <v>8.882853762770537e-06</v>
+        <v>0.06088055670261383</v>
       </c>
       <c r="CV2" t="n">
-        <v>8.152200280164834e-06</v>
+        <v>0.006461096927523613</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.1156997718208e-06</v>
+        <v>0.09057585150003433</v>
       </c>
       <c r="CX2" t="n">
-        <v>2.433821464364883e-06</v>
+        <v>0.03744291514158249</v>
       </c>
       <c r="CY2" t="n">
-        <v>8.84037945070304e-06</v>
+        <v>0.08988535404205322</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.161441216230742e-06</v>
+        <v>0.013173658400774</v>
       </c>
       <c r="DA2" t="n">
-        <v>6.316018698271364e-06</v>
+        <v>0.003744857152923942</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.363199771731161e-06</v>
+        <v>0.009421995840966702</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.911155661422526e-06</v>
+        <v>0.03170914947986603</v>
       </c>
       <c r="DD2" t="n">
-        <v>8.125567774186493e-07</v>
+        <v>0.02176497876644135</v>
       </c>
       <c r="DE2" t="n">
-        <v>5.485396741278237e-07</v>
+        <v>0.01914111152291298</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.1531119273277e-05</v>
+        <v>0.2129359543323517</v>
       </c>
       <c r="DG2" t="n">
-        <v>9.211257747665513e-06</v>
+        <v>0.09410004317760468</v>
       </c>
       <c r="DH2" t="n">
-        <v>9.813436008698773e-06</v>
+        <v>0.03024084866046906</v>
       </c>
       <c r="DI2" t="n">
-        <v>1.307653928961372e-05</v>
+        <v>0.02637595683336258</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.579666241013911e-05</v>
+        <v>0.04913924634456635</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.767174944689032e-05</v>
+        <v>0.05471272021532059</v>
       </c>
       <c r="DL2" t="n">
-        <v>2.010770913329907e-06</v>
+        <v>0.02310755476355553</v>
       </c>
       <c r="DM2" t="n">
-        <v>5.40644941793289e-06</v>
+        <v>0.11395213752985</v>
       </c>
       <c r="DN2" t="n">
-        <v>7.088686288625468e-06</v>
+        <v>0.0006702635437250137</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.151274995616404e-06</v>
+        <v>0.01302622631192207</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.958208465832286e-06</v>
+        <v>0.04952923953533173</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.471509858674835e-05</v>
+        <v>0.01616841927170753</v>
       </c>
       <c r="DR2" t="n">
-        <v>1.768777906363539e-07</v>
+        <v>0.09003175795078278</v>
       </c>
       <c r="DS2" t="n">
-        <v>1.031712031362986e-06</v>
+        <v>0.1295897215604782</v>
       </c>
       <c r="DT2" t="n">
-        <v>2.097115157084772e-06</v>
+        <v>0.09652963280677795</v>
       </c>
       <c r="DU2" t="n">
-        <v>3.708140866365284e-06</v>
+        <v>0.1193828731775284</v>
       </c>
       <c r="DV2" t="n">
-        <v>4.263193204678828e-06</v>
+        <v>0.07101551443338394</v>
       </c>
       <c r="DW2" t="n">
-        <v>1.109968980017584e-05</v>
+        <v>0.04519199579954147</v>
       </c>
       <c r="DX2" t="n">
-        <v>7.718856068095192e-06</v>
+        <v>0.008535776287317276</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.614095592434751e-06</v>
+        <v>0.04774824529886246</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.959701982443221e-06</v>
+        <v>0.05753422155976295</v>
       </c>
       <c r="EA2" t="n">
-        <v>4.339133283792762e-06</v>
+        <v>0.1954310536384583</v>
       </c>
       <c r="EB2" t="n">
-        <v>8.109380360110663e-06</v>
+        <v>0.1831298917531967</v>
       </c>
       <c r="EC2" t="n">
-        <v>6.356490757752908e-06</v>
+        <v>0.01082090847194195</v>
       </c>
       <c r="ED2" t="n">
-        <v>8.665176210342906e-06</v>
+        <v>0.1552149653434753</v>
       </c>
       <c r="EE2" t="n">
-        <v>2.835877694451483e-06</v>
+        <v>0.03283777460455894</v>
       </c>
       <c r="EF2" t="n">
-        <v>1.061875195773609e-06</v>
+        <v>0.003649428486824036</v>
       </c>
       <c r="EG2" t="n">
-        <v>1.542109998808883e-06</v>
+        <v>0.08178529143333435</v>
       </c>
       <c r="EH2" t="n">
-        <v>1.300104827350879e-06</v>
+        <v>0.02184709161520004</v>
       </c>
       <c r="EI2" t="n">
-        <v>1.709448952169623e-05</v>
+        <v>0.1792266964912415</v>
       </c>
       <c r="EJ2" t="n">
-        <v>3.892303539032582e-06</v>
+        <v>0.00747738778591156</v>
       </c>
       <c r="EK2" t="n">
-        <v>3.830789410130819e-06</v>
+        <v>0.04659878462553024</v>
       </c>
       <c r="EL2" t="n">
-        <v>3.31840510625625e-07</v>
+        <v>0.01297353021800518</v>
       </c>
       <c r="EM2" t="n">
-        <v>8.098965736280661e-06</v>
+        <v>0.01195094734430313</v>
       </c>
       <c r="EN2" t="n">
-        <v>2.10287203117332e-06</v>
+        <v>0.01130571402609348</v>
       </c>
       <c r="EO2" t="n">
-        <v>1.301816519116983e-05</v>
+        <v>0.005508327856659889</v>
       </c>
       <c r="EP2" t="n">
-        <v>4.117928256164305e-07</v>
+        <v>0.08194447308778763</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1.050361061061267e-05</v>
+        <v>0.020667415112257</v>
       </c>
       <c r="ER2" t="n">
-        <v>6.954056516406126e-06</v>
+        <v>0.01067656837403774</v>
       </c>
       <c r="ES2" t="n">
-        <v>4.977816274731595e-07</v>
+        <v>0.005060713738203049</v>
       </c>
       <c r="ET2" t="n">
-        <v>1.393942693539429e-05</v>
+        <v>0.01516121905297041</v>
       </c>
       <c r="EU2" t="n">
-        <v>1.762709189279121e-06</v>
+        <v>0.01422511972486973</v>
       </c>
       <c r="EV2" t="n">
-        <v>4.037556664115982e-06</v>
+        <v>9.942334145307541e-05</v>
       </c>
       <c r="EW2" t="n">
-        <v>3.98511747334851e-06</v>
+        <v>0.02445556968450546</v>
       </c>
       <c r="EX2" t="n">
-        <v>9.857394616119564e-06</v>
+        <v>0.01310351304709911</v>
       </c>
       <c r="EY2" t="n">
-        <v>2.413930587863433e-06</v>
+        <v>0.1126231998205185</v>
       </c>
       <c r="EZ2" t="n">
-        <v>2.347548388570431e-06</v>
+        <v>0.04088637605309486</v>
       </c>
       <c r="FA2" t="n">
-        <v>1.099234214052558e-05</v>
+        <v>0.08199764788150787</v>
       </c>
       <c r="FB2" t="n">
-        <v>3.821362952294294e-06</v>
+        <v>0.002753033768385649</v>
       </c>
       <c r="FC2" t="n">
-        <v>4.496655492403079e-06</v>
+        <v>0.02564755082130432</v>
       </c>
       <c r="FD2" t="n">
-        <v>1.814566985558486e-08</v>
+        <v>0.01074583642184734</v>
       </c>
       <c r="FE2" t="n">
-        <v>1.511655909780529e-06</v>
+        <v>0.02900508418679237</v>
       </c>
       <c r="FF2" t="n">
-        <v>2.853957084880676e-06</v>
+        <v>0.01682441867887974</v>
       </c>
       <c r="FG2" t="n">
-        <v>6.426460458897054e-06</v>
+        <v>0.004901647567749023</v>
       </c>
       <c r="FH2" t="n">
-        <v>1.32142131405999e-05</v>
+        <v>0.1063291132450104</v>
       </c>
       <c r="FI2" t="n">
-        <v>1.5841521872062e-06</v>
+        <v>0.09853322803974152</v>
       </c>
       <c r="FJ2" t="n">
-        <v>5.894658443139633e-06</v>
+        <v>0.08623126894235611</v>
       </c>
       <c r="FK2" t="n">
-        <v>8.395975783059839e-06</v>
+        <v>0.03126994147896767</v>
       </c>
       <c r="FL2" t="n">
-        <v>1.755834091454744e-06</v>
+        <v>0.06690762937068939</v>
       </c>
       <c r="FM2" t="n">
-        <v>6.315450718830107e-06</v>
+        <v>0.07846124470233917</v>
       </c>
       <c r="FN2" t="n">
-        <v>2.525113359297393e-06</v>
+        <v>0.2102759480476379</v>
       </c>
       <c r="FO2" t="n">
-        <v>8.478817221657664e-07</v>
+        <v>0.1282581835985184</v>
       </c>
       <c r="FP2" t="n">
-        <v>1.847869134508073e-05</v>
+        <v>0.09379440546035767</v>
       </c>
       <c r="FQ2" t="n">
-        <v>1.057355984812602e-05</v>
+        <v>0.009550359100103378</v>
       </c>
       <c r="FR2" t="n">
-        <v>4.664779680751963e-06</v>
+        <v>0.1766897737979889</v>
       </c>
       <c r="FS2" t="n">
-        <v>1.937883098435123e-06</v>
+        <v>0.1693675518035889</v>
       </c>
       <c r="FT2" t="n">
-        <v>2.212112121924292e-06</v>
+        <v>0.1476863324642181</v>
       </c>
       <c r="FU2" t="n">
-        <v>5.856974894413725e-06</v>
+        <v>0.1336749196052551</v>
       </c>
       <c r="FV2" t="n">
-        <v>2.627247340569738e-05</v>
+        <v>0.001127786003053188</v>
       </c>
       <c r="FW2" t="n">
-        <v>1.648759644012898e-05</v>
+        <v>0.06539814174175262</v>
       </c>
       <c r="FX2" t="n">
-        <v>1.746491875564971e-06</v>
+        <v>0.02184700407087803</v>
       </c>
       <c r="FY2" t="n">
-        <v>1.956421874638181e-05</v>
+        <v>0.02570200711488724</v>
       </c>
       <c r="FZ2" t="n">
-        <v>3.196387751813745e-06</v>
+        <v>0.08756592869758606</v>
       </c>
       <c r="GA2" t="n">
-        <v>1.750400588207413e-05</v>
+        <v>0.02147125080227852</v>
       </c>
       <c r="GB2" t="n">
-        <v>6.589405074919341e-07</v>
+        <v>0.02386986836791039</v>
       </c>
       <c r="GC2" t="n">
-        <v>9.289563422498759e-06</v>
+        <v>0.04455610737204552</v>
       </c>
       <c r="GD2" t="n">
-        <v>1.056485416484065e-05</v>
+        <v>0.06282763928174973</v>
       </c>
       <c r="GE2" t="n">
-        <v>1.402674479322741e-05</v>
+        <v>0.05170446634292603</v>
       </c>
       <c r="GF2" t="n">
-        <v>9.819170372793451e-06</v>
+        <v>0.00793857779353857</v>
       </c>
       <c r="GG2" t="n">
-        <v>7.511147487093695e-06</v>
+        <v>0.03744128718972206</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.02129056304693222</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.004225135315209627</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.004814846441149712</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.007655495777726173</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.01096472889184952</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.005963142029941082</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.01494901813566685</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.00751469237729907</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.006513264961540699</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.02586808986961842</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.006105282343924046</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.006666484754532576</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.005278405733406544</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.001967722782865167</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.006286036223173141</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.02170019969344139</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.005433001555502415</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.01498349476605654</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.0007288214401341975</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.001498909667134285</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.003903520526364446</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.0004010728443972766</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.004661419428884983</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.007065026555210352</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.001438771840184927</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.0004113515606150031</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.0002474085194990039</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.0001378358574584126</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.005138666369020939</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.0001032196450978518</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.000389699125662446</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.01099254935979843</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.006473205052316189</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.0005213820841163397</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.003085491247475147</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.00132197851780802</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.004441536962985992</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.004258628468960524</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.002949246903881431</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>4.29847277700901e-05</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.001819957513362169</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.0009863744489848614</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.001174490666016936</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.001194024458527565</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.002012733835726976</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.01755192503333092</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.004304440692067146</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.002358606085181236</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.002399398479610682</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.007945986464619637</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.001129804295487702</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.00871763564646244</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.006467505823820829</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.001724489382468164</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.006532822735607624</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.004814865067601204</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>0.002694097347557545</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.002856128383427858</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.0001390511752106249</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.002085436834022403</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.0002453322522342205</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.005275581497699022</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.003467660397291183</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.003122491063550115</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.0002232042606920004</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.001749138929881155</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.002340133767575026</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.002777298912405968</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.0002236427972093225</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>0.001845301827415824</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.002345590619370341</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.002553711645305157</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.009311490692198277</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.001703966641798615</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.007423254195600748</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.002576501108705997</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.006486393511295319</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>0.002214472275227308</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.003985663875937462</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.0008781162323430181</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.002617360092699528</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.007375937420874834</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.003326163161545992</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.0008700392208993435</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.001886697020381689</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.003269261913374066</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>0.001691597746685147</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.003789031412452459</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>0.000877021870110184</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.0008676832658238709</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.00252296612598002</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.01519520580768585</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.00842653401196003</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.005448782816529274</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.006588132120668888</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.01248589996248484</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.006577573716640472</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.004847050178796053</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.0006342215929180384</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.006732875015586615</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.003216381650418043</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.0009777249069884419</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.002233762759715319</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.004991691559553146</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>0.002605085028335452</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.004430949222296476</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>0.0001045702374540269</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.001344776363112032</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.001540842931717634</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.00644318014383316</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.002170318737626076</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.002626022789627314</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.01361882034689188</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.0008599072461947799</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.003421083558350801</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.001150891999714077</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.001394226914271712</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.002673598937690258</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.00138950627297163</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.0009899217402562499</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.001087155425921082</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.001024961704388261</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.002780231880024076</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.002786438446491957</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.003233856288716197</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.00496929045766592</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.0006942924810573459</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.007389555685222149</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.0008002328686416149</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>0.0002303063520230353</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.006335597485303879</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.007726256735622883</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.008280439302325249</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.007174272555857897</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>0.004991839174181223</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.005595223046839237</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.0034037996083498</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.001348024583421648</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.007843697443604469</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>3.226716944482177e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>0.0001453717268304899</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.003392872167751193</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.002038812031969428</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>7.39677925594151e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.006207921542227268</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>0.002816170919686556</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.004105300642549992</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.002960823941975832</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.008578023873269558</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.0005084197036921978</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.003772211261093616</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>0.002818853128701448</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.003676705295220017</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.00864378921687603</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.005251393653452396</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>0.0002341074869036674</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.001875250367447734</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.004093904048204422</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.0001201082195620984</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.004855613224208355</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.0009703316609375179</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.0003934699052479118</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.007365840021520853</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.0007542250095866621</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.003774742828682065</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.002877205144613981</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.002940650563687086</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.0001582625554874539</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.003297981806099415</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.002498059067875147</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.003180777654051781</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.009493980556726456</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.004745575599372387</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.009945821948349476</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.006658908445388079</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.01179176196455956</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.008257222361862659</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.006364218425005674</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.00473977904766798</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.00802069716155529</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.003576172981411219</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.001676106010563672</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.002177320886403322</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.003189084120094776</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.002501548733562231</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.01407532021403313</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.007087199483066797</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.002043172717094421</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>0.002928230445832014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.4734476208686829</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.264108896255493</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1160354763269424</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1411204189062119</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5295499563217163</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.179445624351501</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2520780563354492</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2469306588172913</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.06780924648046494</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3077126145362854</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.319872856140137</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1874877214431763</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1713320910930634</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.02294814586639404</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.9945083260536194</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0668313056230545</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2745238542556763</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1064633578062057</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1780031472444534</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2260535359382629</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3215277194976807</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2137729823589325</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1778473854064941</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1024848446249962</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4905382990837097</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.1468353420495987</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1034391298890114</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3854825794696808</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3199979662895203</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.08597438037395477</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.7955889105796814</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.2293428331613541</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.4453204274177551</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3326531648635864</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.5019266605377197</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3671573102474213</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.1463125348091125</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.138353705406189</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.08515803515911102</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.08161332458257675</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.07493652403354645</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.2880843281745911</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.3218183815479279</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.1816767454147339</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.04691976308822632</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.1558626741170883</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.6276228427886963</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.3154215514659882</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.1067065298557281</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.5486311316490173</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.8253631591796875</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.2786748111248016</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.07755348086357117</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.2817538976669312</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.02945078909397125</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.6527951955795288</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.2437527179718018</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.4539548456668854</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.5690257549285889</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.4245371222496033</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.07400505244731903</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.2738135755062103</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.06299270689487457</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.0809771716594696</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.09535884112119675</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.03355621173977852</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.03033605217933655</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.1365677565336227</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1749203056097031</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.07046568393707275</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.1352584511041641</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.134924441576004</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.1376282870769501</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2866075038909912</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.3394682109355927</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.1949792802333832</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.1505420356988907</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.5363730788230896</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.579698383808136</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.04930185526609421</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.03417286276817322</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.0009607821702957153</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.3747393488883972</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.003671254962682724</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.1073454767465591</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.1196279376745224</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.230155736207962</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.04958808422088623</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.03210480511188507</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.007660641334950924</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.4537839591503143</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.556526780128479</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0.5855656862258911</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0.3973742127418518</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.005697526037693024</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.3552330732345581</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.02170940302312374</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.2307085990905762</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0.2211320102214813</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.02157241106033325</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.3505416512489319</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0.05908185988664627</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.06642427295446396</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.1082955300807953</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1959396749734879</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.08237449079751968</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.00428595207631588</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0.001942398026585579</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.5461684465408325</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.07102750241756439</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.3435071408748627</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.1330363601446152</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.1405085325241089</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>1.014403343200684</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0.1444818079471588</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.2260982543230057</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0.2593465447425842</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.07907795906066895</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.3269822001457214</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0.1633400022983551</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.2392155081033707</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.01776959374547005</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.03544570133090019</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.09819680452346802</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0.09747392684221268</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0.1356019526720047</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.1423487365245819</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.2657944560050964</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0.02604670077562332</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0.1277524828910828</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.3518345952033997</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.3825618326663971</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0.0809423103928566</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0.5835343599319458</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0.5094408988952637</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0.07704057544469833</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.1185527145862579</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0.1372530311346054</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.4854804277420044</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.1155830323696136</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.1781745404005051</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0.154859721660614</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0.1368592381477356</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>0.05514524132013321</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0.004102624952793121</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.2302739322185516</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0.3020510077476501</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0.3301185965538025</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>0.4301463961601257</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.4450967311859131</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0.03498032689094543</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>0.2043362557888031</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0.07525360584259033</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0.007079295814037323</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.3389172852039337</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0.05754022300243378</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0.0662178248167038</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0.1690272390842438</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.2137067764997482</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0.02768660150468349</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0.002621920313686132</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0.04675224423408508</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0.2199355363845825</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.03129559755325317</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0.2582477927207947</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0.04503094777464867</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.2464817464351654</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.4436469376087189</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0.1436745226383209</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0.194775179028511</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0.6961285471916199</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0.62666916847229</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.1519169807434082</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0.2064088433980942</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0.0008331835269927979</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.02382605895400047</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.06011537089943886</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0.2793034911155701</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0.1896528303623199</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0.0478794276714325</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0.168124794960022</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.06401866674423218</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0.1994176357984543</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0.009212047792971134</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>0.6142805814743042</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.2453185468912125</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0.2260955274105072</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0.2579905986785889</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0.2663045823574066</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.3356524109840393</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9763630628585815</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2149161994457245</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.09452527761459351</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2503415644168854</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.962409496307373</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1836838126182556</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2859002351760864</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1895311623811722</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.189899355173111</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.215216755867004</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2373963594436646</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1416306346654892</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5617311596870422</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.9575085043907166</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1888386011123657</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.09305372834205627</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1977183818817139</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.06814555823802948</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1200376525521278</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1553641557693481</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.4102492928504944</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.3657766580581665</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.2128164321184158</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.02192604541778564</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1642517298460007</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1819050312042236</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.0312773808836937</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.2140324711799622</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.1261666715145111</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2184398323297501</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.4633283615112305</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.06250950694084167</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.08668350428342819</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.5803517699241638</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.08578290790319443</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.06163298711180687</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2817416191101074</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.149472564458847</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.2410622090101242</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1588646918535233</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.03147982060909271</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.1045831367373466</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.2090786099433899</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.2826665341854095</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.1458162665367126</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.198983788490295</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.1933250427246094</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.09962127357721329</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.300975501537323</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.3902897536754608</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.09370718896389008</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.002235180698335171</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.20353102684021</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.04901048541069031</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.1749275028705597</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.1927468776702881</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.02898816764354706</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.1243370324373245</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.04605312645435333</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.159678190946579</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.1874452233314514</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.04572604224085808</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.08280085027217865</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.1628786027431488</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.02435776963829994</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.2826490700244904</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.1245635747909546</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.1192962229251862</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.5723201632499695</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.05266641080379486</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.1104259118437767</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.01265840977430344</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.709388256072998</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.1427141577005386</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.3932761549949646</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.2419064044952393</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.3874387741088867</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.09218353033065796</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.02699802443385124</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.2028629779815674</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.04062953591346741</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.3558281064033508</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.02309670113027096</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.1146025359630585</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.001208484172821045</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.2282098084688187</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.1795957088470459</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.07199405133724213</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.06330067664384842</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.2539970874786377</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.5225335955619812</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.2346941977739334</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.3298797607421875</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.1399623453617096</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.07930782437324524</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.1437620520591736</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.1033069044351578</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.03130590915679932</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.02351387590169907</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.3010271191596985</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.03416318446397781</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.07299099117517471</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.03343181312084198</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.2435646951198578</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.139598935842514</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.07120160758495331</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.06338629126548767</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.1585585623979568</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.08917266130447388</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.1687839478254318</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.0485728532075882</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.2744118571281433</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.100015789270401</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0.07848662137985229</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.1934839487075806</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0.006490141153335571</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.06634310632944107</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0.1809388399124146</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.05124292150139809</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.09197736531496048</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.1100334972143173</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.1436581313610077</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.1071790754795074</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0.221896693110466</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0.1209535822272301</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0.1086490899324417</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.09359629452228546</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.1261745393276215</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0.1813984364271164</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.1877804100513458</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.3156367540359497</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0.05555788055062294</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0.1706344038248062</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0.2038713097572327</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0.01247839070856571</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0.04199456423521042</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.06967119127511978</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.438794732093811</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0.06427395343780518</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.1634915173053741</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0.06188992038369179</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0.04198191314935684</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0.08943718671798706</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0.007195405662059784</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0.1443990468978882</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0.05504763126373291</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0.01691759750247002</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.07133682817220688</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.05709085986018181</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0.04786690697073936</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0.006787613034248352</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0.05908811837434769</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0.02632255479693413</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.3662668764591217</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.03292853385210037</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.0817323699593544</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.0189763531088829</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.2375870645046234</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0.1908318251371384</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0.09856554120779037</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0.006020085420459509</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0.01575890555977821</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.3285084366798401</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.1538925170898438</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.06358145177364349</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.1068119555711746</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.3189341127872467</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0.1673669219017029</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0.5877062678337097</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0.170174777507782</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0.2033279985189438</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.3475744724273682</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.2468702644109726</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.4066770672798157</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.0210463460534811</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.471140444278717</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0.3004314303398132</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0.3618216216564178</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0.198940247297287</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0.1184995397925377</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0.001078877598047256</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.1722245216369629</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0.1038773357868195</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0.3039806187152863</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.2485825568437576</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0.086262047290802</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0.158463254570961</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0.1764787435531616</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.4392859935760498</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6399493813514709</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2595624625682831</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2167965769767761</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.007600963115692139</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.783980131149292</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2396616637706757</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3080353140830994</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.13418810069561</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.384915679693222</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8146223425865173</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3415819406509399</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.04920880496501923</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2553846836090088</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7572141885757446</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1796622574329376</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.07610749453306198</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3534828722476959</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.07387109100818634</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.04464066401124001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1593345701694489</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.241178497672081</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1982355862855911</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.12783282995224</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.03074217215180397</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1001880168914795</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1579966247081757</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1021494939923286</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.2429634928703308</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.04532692581415176</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2665074467658997</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.2138138115406036</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.1301049590110779</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.01277598366141319</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3934965431690216</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.04577713459730148</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.1387176662683487</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1523566246032715</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.1963361650705338</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.1942552775144577</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.03560381382703781</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.07552774995565414</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.04361109435558319</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.1642045825719833</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.1049237623810768</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.235355943441391</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.7385873794555664</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.2281174063682556</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.09803454577922821</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.1437657624483109</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.443059504032135</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.02411211468279362</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.1021454483270645</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.1012134328484535</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.08381849527359009</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.04658640176057816</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.2183046638965607</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.1079693585634232</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.03047322854399681</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.1764531582593918</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.05461906641721725</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.1801838427782059</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.04962503910064697</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.0316433385014534</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.2004177570343018</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.03460606187582016</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.1253279745578766</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.1567718237638474</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.1231419742107391</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.3560345768928528</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.02790152095258236</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.1610225886106491</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.09940312802791595</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.4299003481864929</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.14873206615448</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.2342499494552612</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.07930315285921097</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.3178680241107941</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.04786019027233124</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.01473817229270935</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.14047871530056</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.07719330489635468</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.2345376312732697</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.008616507053375244</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.1168731153011322</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.05980728566646576</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1835647374391556</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.1169898509979248</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.0636063739657402</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.06118911504745483</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.06194765120744705</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.3613015115261078</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.1992527395486832</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.1586348414421082</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.04163040220737457</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.05447456240653992</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.1165470704436302</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.1299073398113251</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0.01104394532740116</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.04093851521611214</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.2054843604564667</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.01973795518279076</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.08504937589168549</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.03300058469176292</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1769415736198425</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.07279904931783676</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.08603060990571976</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.05729862302541733</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.09397981315851212</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.1030366197228432</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.1157534569501877</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.04885771125555038</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.2071312665939331</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.2007308453321457</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0.06563782691955566</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.2657958269119263</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.01561220735311508</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.07244974374771118</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.1269526928663254</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0.1059310585260391</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.1224178969860077</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.01795019768178463</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.2429909855127335</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.05208070203661919</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.1980894953012466</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0.1026479154825211</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.07983875274658203</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.06177696213126183</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0.1188257411122322</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.1179050281643867</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.1239312812685966</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.2048439681529999</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0.009244523942470551</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.07198439538478851</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0.2482459843158722</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0.1104641705751419</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0.00411556288599968</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0.1106388047337532</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.1431114375591278</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.08123764395713806</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.08822204172611237</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0.04475591331720352</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.03151923790574074</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0.03897936269640923</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0.0389939621090889</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.0887613371014595</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0.01724938116967678</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0.2135855853557587</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.1529281437397003</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1841504275798798</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0.03020718693733215</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0.03757163137197495</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0.05656673014163971</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0.06472175568342209</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.2625247240066528</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0.02365783229470253</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.08201619237661362</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.07834888994693756</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1716438680887222</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0.1116441935300827</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0.07787148654460907</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0.01078111119568348</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0.02819685265421867</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.2719213962554932</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0.1570382714271545</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.0961698517203331</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.09635580331087112</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.3005591630935669</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0.09358377754688263</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0.4242175817489624</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0.2676360011100769</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0.07159741222858429</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.2003314793109894</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0.4126191139221191</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.228419154882431</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.03201362118124962</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.2083314061164856</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0.07988501340150833</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0.2684637904167175</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0.04893916472792625</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.06216094270348549</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.1045625284314156</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.1374664902687073</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0.07934267073869705</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.3134433627128601</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.2172020524740219</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0.03965910151600838</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0.05441455543041229</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.1981233209371567</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.001130154123529792</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002207408659160137</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.141864964272827e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.683312050066888e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0003612947184592485</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0006035675760358572</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001728126226225868</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.636333324015141e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0002486628363840282</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0008232090622186661</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002150537213310599</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.063447704538703e-06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002594733668956906</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.000816796557046473</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.000849257514346391</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0001861118071246892</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9.457601117901504e-05</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0008530351333320141</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0001425113150617108</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.0001218706893268973</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0003597397590056062</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0001696370163699612</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.0005156976403668523</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0003615615714807063</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0002453189808875322</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.000319820421282202</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.0001442565699107945</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.000104528822703287</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.0002578299609012902</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6.432451482396573e-05</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.0008363391389138997</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0007773931138217449</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.000320778985042125</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0002895703946705908</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0002800703514367342</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.000172194981132634</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0003963366325479001</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0002653889241628349</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.000284541049040854</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.0005438963416963816</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>4.253021324984729e-05</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0002270023978780955</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.0002843600523192436</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.294104191008955e-05</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.0001703331072349101</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.0006196940084919333</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.001161692081950605</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>7.495254976674914e-06</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.0001288117637159303</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.0004827772499993443</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.0005092809442430735</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6.536506407428533e-05</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.0003174292796757072</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.0003173446166329086</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0004420936165843159</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0007327644852921367</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.0004557273932732642</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.0001182561682071537</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.0003419757995288819</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.0003030371735803783</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.0003374071966391057</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0001038872578646988</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.54636465292424e-05</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.0001873833825811744</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>3.63982398994267e-05</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.326855171006173e-05</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>7.773497782181948e-05</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0004440218908712268</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>9.091740503208712e-05</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.0002822502865456045</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>6.919955194462091e-05</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0003868310304824263</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.000804924638941884</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.0007481626234948635</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.0001675037201493979</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1.713295932859182e-05</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.534234615974128e-05</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.0006631904980167747</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0002025852154474705</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>9.567057713866234e-05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.0002573229430709034</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.0004112734750378877</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.0006375923403538764</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.000130017040646635</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.0001104007533285767</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>7.557076969533227e-06</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.000213011444429867</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.0001235045492649078</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.057683766703121e-05</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.0001445768866688013</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>1.765452907420695e-05</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.000650784932076931</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0004487033875193447</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0001694466336630285</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.0005878469673916698</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0006207390688359737</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.0001565088605275378</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>3.801188722718507e-05</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1.891083957161754e-05</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.0003574657603166997</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.0005981912836432457</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.0001332203537458554</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>2.708053216338158e-05</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>8.322840585606173e-05</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0002356410841457546</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>3.865271082759136e-06</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.0001987892319448292</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>9.498880535829812e-05</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>6.54339964967221e-05</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.0003746866132132709</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>6.389536429196596e-05</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.000115502392873168</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.0008618617430329323</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>2.646551001816988e-05</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.0001897257461678237</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.0002966104948427528</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.0002811695740092546</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0001175118086393923</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.0004655059310607612</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.0002017381630139425</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0001145063724834472</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.0003460030420683324</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0004594305937644094</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>2.000182030315045e-05</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.0005436681676656008</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.0003343974240124226</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.0001874917943496257</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0002388751454418525</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>7.645212463103235e-05</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0003143547801300883</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.0001179263272206299</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>9.765414870344102e-05</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.000117729272460565</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0005134161910973489</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.0001236010575667024</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.0003616848553065211</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.0001129793381551281</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.0002648369700182229</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>9.905017577693798e-06</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>9.174465230898932e-05</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0001233044022228569</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>2.289516487508081e-08</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>8.282460476038978e-05</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>7.037426985334605e-05</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.0005112480721436441</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.0002370144939050078</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.0002517238899599761</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.0001603999553481117</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.0004096173797734082</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.0005098386318422854</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.0001271576475119218</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>4.264519520802423e-05</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.0003317557566333562</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.0004500996728893369</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.0006538751185871661</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>7.533359894296154e-05</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>4.576408537104726e-05</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>9.313886403106153e-05</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.0001711368386168033</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.0001220335980178788</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>9.162919013760984e-05</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>3.848558480967768e-05</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>9.106037032324821e-05</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.0004666538152378052</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.0002265999210067093</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.000167317979503423</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>1.174163116957061e-05</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.0005277544842101634</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>9.027598025568295e-06</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.0001474239688832313</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.0003710189484991133</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.0004864974762313068</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.0008413111208938062</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.0001886908867163584</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.000604482542257756</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.0001411553530488163</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.0006157339084893465</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.000349692563759163</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.0005405659321695566</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.0002664165804162621</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.0004861457273364067</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>6.02153450017795e-05</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.0002635903656482697</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.000212097744224593</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0.0001292763336095959</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.000448875711299479</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.0003596503811422735</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>9.030693036038429e-05</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.000436952686868608</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.002449591876938939</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01180689688771963</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.006333410739898682</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.002153316978365183</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.003295013913884759</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.00123769708443433</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.004823649302124977</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0008207320934161544</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0005659093731082976</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0003314344212412834</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0112400883808732</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.002081280341371894</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0006264839321374893</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.008667674846947193</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.002130839042365551</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.00466751167550683</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0009304691338911653</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.002629802096635103</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.500391125679016e-06</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.004675911739468575</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.001300881034694612</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.00245127291418612</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.002755788620561361</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.001109464908950031</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.000666717067360878</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.001450908719561994</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.0004507346311584115</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.001712537370622158</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.003249448956921697</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.001167936599813402</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.002833601785823703</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.002898694947361946</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.00451168417930603</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.00213332730345428</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.003688592929393053</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.0007676998502574861</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.002832913771271706</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.002259489148855209</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>8.358038030564785e-06</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.00199957238510251</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.006806571036577225</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.001963459886610508</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.001270628301426768</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.005430259741842747</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.920293137431145e-05</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.001797499600797892</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.0110936276614666</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.0008356997277587652</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.001509561436250806</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.005736707244068384</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.00705326534807682</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.001374741201288998</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.001425244146957994</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.00285863783210516</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.003591954009607434</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.01385133806616068</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.004561104811728001</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.001155451755039394</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.01331038773059845</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.003363907570019364</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.005478531587868929</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.007965119555592537</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.002106659114360809</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.001153469318524003</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.002438168041408062</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.003155654529109597</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.002536940854042768</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.004473409149795771</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.0006326650036498904</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.0001222388818860054</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.005597012117505074</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.001850970322266221</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.0004586047725751996</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.01528394594788551</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.000963553786277771</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.006096016615629196</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.004229806363582611</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>3.013538662344217e-05</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.002026035217568278</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.001496678218245506</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.001005349098704755</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.000189661150216125</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.0047318902797997</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.002544619143009186</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>5.699135363101959e-05</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>8.346105460077524e-05</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.0004097632190678269</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.0002836839994415641</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.001132153323851526</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.0006303733680397272</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.0010790741071105</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.0009791271295398474</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.0006038479041308165</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.009701566770672798</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.005837983451783657</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.003286386607214808</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.0006325275753624737</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.007110714912414551</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.001536258729174733</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.001430168864317238</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.0042085787281394</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.002126813400536776</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.0006347086746245623</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.001409020973369479</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.0002437190851196647</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.0001958877837751061</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.0007121722446754575</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.0002632641699165106</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.004173150286078453</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.005241978913545609</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.0008961638668552041</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.008078436367213726</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.01121970638632774</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.003640741342678666</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.001049682148732245</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>6.595111335627735e-05</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.001817090436816216</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.0008594090468250215</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.004155910573899746</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.001906710327602923</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.001141427201218903</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.001288563711568713</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>7.918624032754451e-05</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.0008261594921350479</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.0007743760943412781</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.003754885867238045</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.002665183274075389</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.000471556733828038</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.003916530404239893</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.006441732868552208</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.003520529484376311</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.001544270664453506</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.0009325207793153822</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.003641499672085047</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.006190119311213493</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.0006446340121328831</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.002381460275501013</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.0003675150219351053</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.002305889502167702</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.004028209485113621</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.002410964341834188</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.001200974686071277</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.001725226873531938</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.0005418300279416144</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.003294978756457567</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.002683775033801794</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.0009111651452258229</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.002176539739593863</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.001899738213978708</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.004824067931622267</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.001302425749599934</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.004479761701077223</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.00435841828584671</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.0005735646118409932</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.005026194266974926</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.00219647423364222</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.001266579609364271</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>4.175172944087535e-05</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.0001867898972705007</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>9.74516588030383e-05</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.0007383017800748348</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.0001694541133474559</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.001198737765662372</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.004079670645296574</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>6.436486728489399e-06</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.00310982926748693</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.0001009689876809716</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.00121375685557723</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.0004723328747786582</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.002312956377863884</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.0009707554709166288</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.0006892382516525686</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.008503001183271408</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.01286610867828131</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.00090515345800668</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.00518643856048584</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.006379223428666592</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.003537726821377873</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.005472145974636078</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.0088281175121665</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.003105161944404244</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.004737550392746925</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.0002548056654632092</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.0009064156329259276</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.001153010642156005</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.0008942888816818595</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.0004844178620260209</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.004099898040294647</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.002232101978734136</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.116785824706312e-06</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.039200580838951e-06</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.186507117585279e-07</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.190619963788777e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.855813363566995e-09</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.242391474283068e-06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.926386090644883e-07</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.054016593116103e-06</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.562426335676719e-08</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8.846706691656436e-07</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.943654180853628e-06</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.139099706255365e-07</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7.052535693219397e-07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.083676352209295e-06</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.306495389348129e-06</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.831517917911697e-07</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.662806756845384e-07</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.089297789278135e-08</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.671124145261274e-07</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.060984283820289e-07</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.125971090867097e-07</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.614373784126656e-08</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.784562980195915e-08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9.54095753513684e-07</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.312366689238843e-07</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9.332508170700748e-07</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.379628796234101e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.227415168614243e-06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.540869618565921e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.893755493005301e-07</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.387961212160008e-07</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>9.818895705393516e-07</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4.045756440973491e-07</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>7.264638952619862e-07</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.035802824844723e-06</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.53309557049397e-07</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>9.833294711825147e-08</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>5.651865535583056e-07</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>5.571041583607439e-08</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>5.619331204798073e-07</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.691193401460623e-07</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.292420842626598e-07</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.349411935640092e-08</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>8.496434702465194e-07</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.590475211647572e-07</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.286734345740115e-07</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.022248847628362e-06</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.914063194722985e-08</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.067704478278756e-08</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.068674919224577e-06</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.164078750865883e-06</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5.841229722136632e-08</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.822908354322863e-07</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.540691626672924e-08</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8.67400899551285e-07</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>6.654094590885506e-07</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.694686488917796e-07</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.279171269492508e-07</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.834634180246212e-07</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>6.589110626009642e-07</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.523723535181489e-07</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.73483670096175e-07</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.751663027491304e-07</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>4.386153023006045e-07</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>4.200194894110609e-07</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>2.067672255634534e-08</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5.061530146122095e-07</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>5.495708137459587e-07</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4.072382182584988e-07</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2.974335302496911e-07</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>3.689856384880841e-07</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>2.71850723265743e-07</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>8.315973332173598e-08</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1.514060272711504e-06</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7.094391207829176e-08</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>6.347423777697259e-07</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>2.162945520467474e-07</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1.177025410470378e-06</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>2.097866484973565e-07</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>6.862925374662154e-07</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>6.76240503594272e-08</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>3.956170075980481e-07</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>7.847482947909157e-07</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>1.237718549873534e-07</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>3.551621148289996e-07</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>1.875512651849931e-07</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>6.014267910359195e-07</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.739261534794423e-07</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>6.279059761027384e-08</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>5.042419815026733e-08</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>1.123397851188201e-06</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>9.280821018364804e-07</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.227303982886951e-07</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>1.813082093349294e-07</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>3.24542526186633e-07</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.440207029190788e-07</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>7.247975020163722e-08</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>1.60533588200451e-07</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.990682250152531e-07</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>2.474550910847029e-07</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>6.421874445550202e-07</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>3.280149485362926e-09</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>4.571813292386651e-07</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.278129045407695e-07</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>7.154835657274816e-07</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>2.119742603667873e-09</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>5.37772564257466e-08</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>7.603163965086424e-08</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>4.687250623192085e-07</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>6.739976470271358e-07</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>3.977702647262049e-07</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>2.300800616694687e-07</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>2.736893520705053e-07</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>8.309240797643724e-07</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>7.770236720716639e-07</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>9.750394838192733e-07</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>4.496371275308775e-07</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>1.506747935309249e-07</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>1.168749435009886e-07</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>7.078614316924359e-08</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>2.850413522992312e-07</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>2.943824597423372e-07</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>7.581464274153404e-07</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>8.909183435434898e-08</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>1.002369685920712e-06</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>3.590178891954565e-07</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>4.36279151472263e-07</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>3.138107445010974e-07</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>1.500706048318534e-08</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>6.081774728272649e-08</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>5.438689640868688e-07</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>1.02575450000586e-06</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>6.651437729487952e-07</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>6.435537898141774e-07</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>4.674026286011213e-07</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>4.977181333742919e-07</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>3.459321931131853e-07</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>3.037330031929741e-08</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>1.448887729793569e-07</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>5.430131722050646e-08</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>3.714189347192587e-07</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>7.308925376037223e-08</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>4.563219704323274e-07</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>1.46759944641417e-07</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>1.267957827622013e-07</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>3.07145285205479e-07</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>1.74267569263975e-08</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>1.034988940773474e-06</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>3.085418711634702e-07</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>3.683973091028747e-07</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>2.418339590803953e-07</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>2.700716663639469e-07</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>3.687503351557098e-07</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>3.946990432268649e-07</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>8.025861575333693e-07</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>7.285202485718401e-08</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>3.139290924991656e-07</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>5.212369558194041e-08</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>6.553544835696812e-07</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>1.650466003866313e-07</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>1.135052940526293e-07</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>1.555424660182325e-07</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>1.883592801732448e-07</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>6.056246775187901e-07</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>6.976542010761477e-08</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>2.396830893758306e-07</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>5.613359377321103e-08</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>1.754817589016966e-07</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>7.124647538603313e-08</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>8.219491860472772e-07</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>6.569575816683937e-08</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>2.007852941687815e-07</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>6.302001764879606e-08</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>3.661272955923778e-07</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>2.37329928154395e-07</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>8.078336577455048e-07</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>7.517078870478144e-08</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>1.17279546429927e-06</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>1.060847580447444e-06</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>1.34135547114056e-07</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>7.685537752877281e-07</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>1.392509432207589e-07</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>5.701242571376497e-07</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>4.812918064089899e-09</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>8.002480740287865e-07</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>6.809663091189577e-07</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>6.078305148093932e-08</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>6.908695695528877e-07</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>4.901726811112894e-07</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4.216656463995605e-07</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.891891088234843e-06</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.566608708955755e-07</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.153223459179571e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.775999519144534e-07</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.300212488786201e-06</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.427289078037575e-07</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.284616809651197e-07</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.510827184527443e-08</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.442824774741894e-07</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.030582209044951e-06</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8.479977395836613e-07</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.214412009176158e-06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.422763998310984e-07</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.150583784692571e-06</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6.203177349561884e-08</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.342170120073206e-07</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6.352083659066921e-08</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.315315785177518e-07</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.032710486015276e-07</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.464578301442089e-07</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.156343643060609e-07</v>
+      </c>
+      <c r="W13" t="n">
+        <v>5.198791441785033e-08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5.162021921023552e-07</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4.167821998635191e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.792699736024588e-09</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.035733359662117e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.385733696679381e-07</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.417499610553932e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.336402704055217e-07</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.330586141852109e-07</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.871996341331396e-07</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>6.308783895292436e-07</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.424224187005166e-08</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.575102999140654e-07</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.428718476859103e-08</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.549700812120136e-09</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>3.367463250469882e-07</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>3.911269459422329e-07</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.965995520298748e-07</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3.250612508054473e-07</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.942078308227792e-07</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7.026044102076412e-08</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.912111440878107e-08</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.958142945568397e-07</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.685404254521018e-08</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>9.374487035529455e-07</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.496802835594281e-07</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.453665039567568e-07</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.674328811735904e-07</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6.011218260937312e-07</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>7.106052635208471e-09</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.016093578864457e-08</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.957058799462175e-07</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8.306614063258166e-08</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.983028994345659e-07</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>3.325201021198154e-07</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>6.048349376897022e-08</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.9203833896172e-07</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1.190429017583483e-07</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.072205683769425e-09</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.661530291130475e-08</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.728676579659805e-08</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>5.898995958375508e-09</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.686557820652524e-08</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.529858764115488e-07</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>6.849776212902725e-08</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9.462621619604761e-08</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>2.697851755328884e-07</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1.374805407294843e-07</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.578437434091029e-07</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1.460267355923861e-07</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.799853919237648e-07</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>3.89555452784407e-07</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>2.823740601343161e-07</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>3.64398118790632e-07</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.743945006182912e-07</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>6.354330253088847e-07</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>6.944620878357455e-08</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>3.03038554250179e-08</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>1.281367758565466e-07</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>1.096350477070018e-08</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>5.913832978876599e-07</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>1.431437794963131e-07</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>2.935323379915644e-07</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>8.675694118664978e-08</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>2.28908191957089e-07</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.348152167679473e-08</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.147785084754105e-07</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.05841388378758e-08</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>1.811030756471155e-07</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.118500279062573e-07</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>6.099618303778698e-07</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>2.749067391505378e-07</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>1.476366584540756e-08</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>2.936010332632577e-07</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>1.276332426414228e-07</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>1.551470205640726e-07</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.443148960333929e-07</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>5.506678490974082e-08</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>5.633257842418971e-07</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.68967503100248e-07</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>3.26490095403642e-07</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.153868905452327e-08</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>2.780667216484289e-07</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.570250596216738e-08</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>1.299531504628249e-07</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>1.025136775467672e-08</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>2.484140111391753e-07</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>3.418775804675533e-07</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>4.268692634923354e-07</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>1.009492649473032e-07</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>1.733666579184501e-07</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>7.814643367964891e-07</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>6.947342257035416e-09</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>6.811382604610117e-07</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>2.023245713189681e-07</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>6.04394134740005e-09</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>3.956315026698576e-07</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>1.186931655183798e-07</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>1.715937401058909e-07</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>1.798948972009384e-07</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>2.933729774667881e-07</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>5.528870516968709e-08</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>1.715621351650043e-07</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>3.479282497664826e-07</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>2.460159578276944e-07</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>1.498188453297189e-07</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>2.750518035554705e-07</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>2.682945137166826e-07</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>3.602542335556791e-07</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>3.720265908668807e-07</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>1.321661535769181e-08</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>5.939212428529572e-07</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>4.461887783691054e-07</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>9.473609452470555e-08</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>5.089538035463193e-07</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>8.837271536776825e-08</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>2.538365322379832e-07</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>2.829539269555426e-08</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>1.965609186527217e-07</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>4.84232245412386e-08</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>7.534801227393473e-09</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>4.643752760102871e-08</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>1.6057680340964e-07</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>3.021986287876643e-07</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>9.861253147391835e-08</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>3.007880877703428e-07</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>8.245269356166318e-08</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>2.286779476889933e-07</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>1.979936854468178e-07</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>2.101041047808394e-07</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>2.496711886124103e-07</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>1.465255561328149e-08</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>6.596752086807101e-07</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>1.293866205287486e-07</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>3.35407321472303e-07</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>8.24216712658199e-08</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>3.140421256375703e-07</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>7.109738575650226e-09</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>1.642116700395491e-07</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>3.115533431241602e-08</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>8.959909791883547e-08</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>2.099041154224324e-07</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>1.103906228649976e-07</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>3.400375874207384e-07</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>2.9393822842394e-07</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>1.956264128466501e-07</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>1.604135206889623e-07</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>4.627302629955921e-08</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>1.198214079067839e-07</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>1.458091674066964e-07</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>3.963477865909226e-07</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>2.4065263914963e-07</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>1.927532764511852e-07</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>2.497646960364364e-07</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>1.498499528906905e-07</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>1.952494415036199e-07</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>3.255801672708003e-08</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>5.403398972703144e-07</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>6.379403316714161e-08</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>1.772328914739774e-07</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>2.116142638897145e-07</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>1.39190063919159e-08</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>7.504638688260457e-08</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>3.912062140898342e-07</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>1.741298092383659e-07</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>2.943938000044e-07</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>2.475290905579186e-08</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.1085646823048592</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.021109223365784</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0380321741104126</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2766221761703491</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5042160749435425</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8180153369903564</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4130997359752655</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.146449446678162</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2431680858135223</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.05473300814628601</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.200941681861877</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2245233952999115</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5455113649368286</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.439121603965759</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.9781197905540466</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2848686575889587</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.9392232298851013</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3916301131248474</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.165513664484024</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.2361571788787842</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1088635548949242</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4232285618782043</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.2461090981960297</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1713123321533203</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1142114326357841</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.1605732589960098</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.001814901828765869</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.2231440842151642</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.3404627442359924</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.04554818570613861</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.398312121629715</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.3626108169555664</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.2252554893493652</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.0117456242442131</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.3273480236530304</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.2078892439603806</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.2858917713165283</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.3595708310604095</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.1043777242302895</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.06629832088947296</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.1641089767217636</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.2006572484970093</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.1019016429781914</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.2288595587015152</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.06344233453273773</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.1046040207147598</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.94943368434906</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.04747293144464493</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.2424208074808121</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.2319469898939133</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.692006528377533</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.09056589007377625</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.3267459273338318</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.1108988374471664</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.1551438421010971</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.6901437640190125</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.05417690798640251</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.1597884744405746</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.3191340863704681</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.1343685388565063</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.1235750094056129</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.5315117239952087</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.07758221030235291</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.06193191558122635</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.2159051299095154</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.3765617311000824</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.09096748381853104</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.2167304456233978</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.2079620957374573</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.3243005573749542</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.06044743210077286</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.02010261826217175</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.1891173124313354</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.771762490272522</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.03736426681280136</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.4022414982318878</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.364467591047287</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.3395852446556091</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.3224305510520935</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.2762607038021088</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.002202675677835941</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.04341666027903557</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.3388303220272064</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.09429271519184113</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.09824934601783752</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.2175338268280029</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.2301478534936905</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.07661724835634232</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.03777434676885605</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.01373821124434471</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.27439945936203</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.3903340697288513</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.1826540231704712</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.6690869927406311</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.4146171510219574</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.1685066670179367</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.01544108428061008</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.1883959323167801</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.01361189410090446</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.1226556897163391</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.2987266182899475</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.1058980822563171</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.152635931968689</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.2153743952512741</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.301397293806076</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.007592816837131977</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.01255198195576668</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.00973116047680378</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.05121967196464539</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.1843187510967255</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.1124333888292313</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.1714845448732376</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.5169990062713623</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.3893471360206604</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.1140749007463455</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.04539894312620163</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.07905136048793793</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.1715354770421982</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.1657265722751617</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0.098326176404953</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.08442283421754837</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.2406525462865829</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.1745487302541733</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.1819551587104797</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.05007999390363693</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.342274397611618</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.2002217173576355</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.4021744430065155</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0.1245522871613503</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.005681239068508148</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.221304327249527</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.04809956252574921</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0.01918351277709007</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.2437146157026291</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.3440817594528198</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.01384299993515015</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.243061900138855</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.1441054940223694</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.07424475252628326</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.2763164639472961</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.1660359352827072</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.04066352546215057</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.1444746851921082</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0.009055683389306068</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.1469220221042633</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.2221356332302094</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.1697671413421631</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.03646636754274368</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.1545308232307434</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.2529759705066681</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.05733045190572739</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0.0476473942399025</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.2727341055870056</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.09276892244815826</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.3796289563179016</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.06732019037008286</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.1801110208034515</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.1713873445987701</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.282723605632782</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.09903442114591599</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0.03745768964290619</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0.03659624978899956</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.05942150950431824</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1393234729766846</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.25556880235672</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.2675189971923828</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.02069359086453915</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.1761154979467392</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.3110276758670807</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.1338250935077667</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.3310009837150574</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.2161502540111542</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.01737438142299652</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.2100310921669006</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.2516216039657593</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.6156765818595886</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0.157831221818924</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.1772186458110809</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.451951652765274</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.2549871504306793</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.1494167447090149</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.02983042597770691</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.223090648651123</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.1123302578926086</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.1993634104728699</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.04868578910827637</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.1820282340049744</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0.1069272011518478</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.07218153774738312</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6.224520898712171e-09</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.433967776800273e-08</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7.369573395976659e-09</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.504720259504211e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.695457604484091e-09</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.95441520137274e-08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.010105421528351e-08</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.316363018588618e-08</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.17065546145767e-09</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.871360844063474e-09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.444979768119083e-08</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.566345937628284e-09</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.771265445427161e-08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.063836745946901e-08</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.98269924314809e-08</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9.116267740694184e-09</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7.012131320038861e-09</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8.4876811135004e-10</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.351719511992314e-09</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.000417748642235e-09</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5.858960872018315e-09</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.886367920344583e-09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.328655490657638e-09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.763672430321606e-09</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.770023404570111e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.74075776016025e-09</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.962989658656824e-10</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.273885245709153e-09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.276921453249543e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>6.354112791484567e-09</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>4.273011722233377e-09</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.786452846237353e-09</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.016143702514682e-08</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>5.6351046051617e-10</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.347017519748306e-08</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.418164279927026e-10</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>9.786861099314592e-09</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4.683730736587677e-09</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.057637355472707e-08</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9.669072653650801e-09</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.33264643764619e-09</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.012702975979664e-09</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.916981906546766e-09</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.85755036194746e-09</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.699316852845413e-09</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.916015760083383e-09</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.375149499300733e-08</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.169915897492046e-08</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.813591499200129e-10</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.295480605596367e-08</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.709815578010421e-08</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.356769890354826e-09</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.186233111738488e-09</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.199117885685723e-10</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.776397416999089e-09</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.027653404710009e-09</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.455934039995554e-09</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.784549645364677e-09</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>9.551355262260586e-09</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.086213979346496e-10</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.026564249746343e-09</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>8.833731968138636e-09</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.279654826547016e-09</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>4.893857319387962e-09</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>7.965049064750929e-09</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>3.054740238539466e-09</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.534833454248542e-09</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>9.507890474935721e-09</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>4.027750577506595e-09</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>5.954350346115689e-09</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>2.036860902165927e-09</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1.977313646150947e-09</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.277265626598023e-09</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1.145136874214359e-08</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>5.108212519644439e-09</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>3.048882035727729e-09</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>2.613932625905591e-09</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>7.774102250834858e-09</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>6.333361834975904e-09</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>4.872213188455987e-10</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>6.483102943377617e-11</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>7.02118474471547e-10</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>1.013808592631449e-08</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>2.099561857704657e-09</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>4.997730673750311e-09</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>4.093854144571196e-09</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>7.095219967112598e-09</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>2.061553427967766e-10</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>2.823352884817609e-09</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>2.430925905017034e-09</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>5.56362156345358e-09</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>6.054335255356591e-09</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.033741359179885e-08</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>1.064983212728521e-09</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>5.344061859702265e-10</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>4.239418593954269e-09</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>5.627426524767998e-09</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>2.774522611659336e-09</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>2.97581026487137e-09</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>8.384826721830052e-10</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>7.333653684327146e-09</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>2.141454347182048e-09</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>5.781895850986984e-09</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>4.858347946168351e-09</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>7.811181035322079e-09</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>8.756804725784662e-10</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>2.470139648380609e-09</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>2.274209043306996e-09</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>2.319870073819175e-09</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>2.777159169298216e-09</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>3.44703865451379e-09</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>1.555720885448864e-09</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>1.013527395343772e-08</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>1.243188751942625e-08</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>5.939668201726533e-10</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>7.558519143913145e-09</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>5.121461033041896e-09</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>2.648089303391998e-09</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>7.361554033025186e-09</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>7.237191956832589e-10</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>3.064593023793805e-09</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>3.172166140874566e-10</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>6.461346568897852e-09</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>3.837445916587967e-09</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>4.388855501247235e-09</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>3.684062499509366e-10</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>4.802264363945596e-09</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>5.97439697713753e-09</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>9.093434449880533e-09</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>2.080846828178551e-09</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>4.351548454906151e-09</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>3.116037206041256e-09</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>4.061438685365459e-10</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>6.118930695464542e-09</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>4.211619053506865e-09</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>4.050471957839363e-09</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>5.91670179517223e-09</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>7.967781989748346e-10</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>1.738760913028159e-09</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>8.817917063197456e-09</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>7.362300546986944e-09</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>1.448050568342296e-09</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>4.064499015132839e-10</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>4.032383038587994e-10</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>3.438862306026635e-09</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>3.904352841033187e-09</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>3.082781585561634e-09</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>6.785375816775741e-09</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>3.317857988349715e-09</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>1.126289617126019e-09</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>1.816963801637428e-09</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>2.885048200340634e-09</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>2.797726272874002e-09</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>6.854529166488987e-10</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>1.044991293497333e-08</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>2.276616450913593e-09</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>5.602906583135336e-09</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>2.470999849180089e-09</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>7.280291924871563e-09</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>1.604079924444335e-10</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>2.849762426038183e-09</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>5.076716824703453e-10</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>5.117889445571677e-10</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>4.688335941693822e-09</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>8.164887432826617e-09</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>1.836799601306893e-09</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>1.923785797330879e-09</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>6.270942876085428e-09</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>2.674428178917054e-10</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>6.554286002824483e-09</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>8.648035176861413e-09</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>8.501074511002571e-09</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>7.635064136479741e-09</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>1.357596968176722e-08</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>8.581189980816362e-09</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>1.121839177109507e-09</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>6.927312057314339e-10</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>1.449157793764755e-09</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>9.496719854951152e-09</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>1.671906835198911e-09</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>2.098771378911124e-09</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>5.995381968659785e-10</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>8.650861360592899e-09</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>2.811441524031011e-09</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>1.228935264663278e-08</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>9.889638441507032e-09</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>3.087143873869991e-09</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>3.849098373365223e-09</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>3.94390686775381e-10</v>
       </c>
     </row>
   </sheetData>
